--- a/17 18 20/Excel/02.Data Management Data Cleaning/Data Management Data Cleaning.xlsx
+++ b/17 18 20/Excel/02.Data Management Data Cleaning/Data Management Data Cleaning.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1849" uniqueCount="217">
   <si>
     <t>passanger</t>
   </si>
@@ -683,7 +683,10 @@
     <t>Prod-3</t>
   </si>
   <si>
-    <t>Prod-1-Prod-2</t>
+    <t>Sunil</t>
+  </si>
+  <si>
+    <t>Use of $ sign</t>
   </si>
 </sst>
 </file>
@@ -904,7 +907,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1071,6 +1074,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2395,10 +2399,10 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E4" s="62" t="s">
+      <c r="E4" s="63" t="s">
         <v>130</v>
       </c>
-      <c r="F4" s="62"/>
+      <c r="F4" s="63"/>
       <c r="H4" s="29" t="s">
         <v>127</v>
       </c>
@@ -3624,64 +3628,64 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="64" t="s">
         <v>200</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63" t="s">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="64" t="s">
         <v>199</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63" t="s">
+      <c r="B3" s="64"/>
+      <c r="C3" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
       <c r="H3" t="s">
         <v>207</v>
       </c>
-      <c r="I3" s="63" t="s">
+      <c r="I3" s="64" t="s">
         <v>206</v>
       </c>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63" t="s">
+      <c r="B4" s="64"/>
+      <c r="C4" s="64" t="s">
         <v>204</v>
       </c>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="64" t="s">
         <v>199</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63" t="s">
+      <c r="B5" s="64"/>
+      <c r="C5" s="64" t="s">
         <v>205</v>
       </c>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -11202,7 +11206,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:L7"/>
+  <dimension ref="B1:M15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
@@ -11211,7 +11215,7 @@
     <col min="8" max="10" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B1" s="11" t="s">
         <v>212</v>
       </c>
@@ -11221,129 +11225,241 @@
       <c r="D1" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B2" s="11" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="11">
-        <v>1</v>
-      </c>
-      <c r="C2" s="11">
-        <v>1</v>
-      </c>
-      <c r="D2" s="11">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <f>B$2+C2</f>
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <f t="shared" ref="I2:J2" si="0">C$2+D2</f>
-        <v>2</v>
-      </c>
-      <c r="J2">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="H2" t="str">
+        <f>$B$2</f>
+        <v>Sunil</v>
+      </c>
+      <c r="I2" t="str">
+        <f t="shared" ref="I2:M9" si="0">$B$2</f>
+        <v>Sunil</v>
+      </c>
+      <c r="J2" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <f t="shared" ref="I2:L2" si="1">$B$2+F2</f>
-        <v>1</v>
-      </c>
-      <c r="L2">
+        <v>Sunil</v>
+      </c>
+      <c r="K2" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="L2" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="M2" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H9" si="1">$B$2</f>
+        <v>Sunil</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="K3" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="M3" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="H4" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B3" s="11">
-        <f>B2+1</f>
-        <v>2</v>
-      </c>
-      <c r="C3" s="11">
-        <f>C2+1</f>
-        <v>2</v>
-      </c>
-      <c r="D3" s="11">
-        <f>D2+1</f>
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H7" si="2">B$2+C3</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="11">
-        <f t="shared" ref="B4:D7" si="3">B3+1</f>
-        <v>3</v>
-      </c>
-      <c r="C4" s="11">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="D4" s="11">
-        <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="11">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="C5" s="11">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="D5" s="11">
-        <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="11">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="C6" s="11">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="D6" s="11">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="11">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="C7" s="11">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="D7" s="11">
-        <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="2"/>
-        <v>7</v>
+        <v>Sunil</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="K4" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="M4" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="H5" t="str">
+        <f t="shared" si="1"/>
+        <v>Sunil</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="M5" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="H6" t="str">
+        <f t="shared" si="1"/>
+        <v>Sunil</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="H7" t="str">
+        <f t="shared" si="1"/>
+        <v>Sunil</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="H8" t="str">
+        <f t="shared" si="1"/>
+        <v>Sunil</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="H9" t="str">
+        <f t="shared" si="1"/>
+        <v>Sunil</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="K9" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="0"/>
+        <v>Sunil</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="J11" s="62"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="H15" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
